--- a/teste.xlsx
+++ b/teste.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pastores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pastores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Daniel Felix Teixeira</t>
+          <t>Abceil Luiz Da Silva Filho</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19974037220</t>
+          <t>65996500834</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Otávio</t>
+          <t>Abdiel Bibiano Neves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19998016329</t>
+          <t>27996118937</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Teste Erro</t>
+          <t>Abelange Paixão da Silva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>00000000000</t>
+          <t>81994645350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Não enviado</t>
+          <t>Enviado</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Elisa</t>
+          <t>Abias Clemente dos Santos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19999844586</t>
+          <t>11989535903</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Enviado</t>
+          <t>Não enviado</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Abidias Freiria Teixeira</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19996594696</t>
+          <t>11964111782</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,727 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mikael</t>
+          <t>Abimael Araújo Prado</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19999308960</t>
+          <t>85988237772</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Abimael Pereira da Silva</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4196118316</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Evangelista</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Abimael S. Ciriaco</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>63992129617</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Abinadabe Coelho da Silva</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>17997685746</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Abirailto Pereira Da Silva</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>74999948304</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Abnaildo Durães Silva</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>62981338026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Abner Ferreira de Assis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8133148815</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Abner Marcos Carneiro Rodrigues</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12988162229</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Abraão da Silveira dos Santos</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>28998831564</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Abraão Demétrios Ataide de Souza</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>99984897945</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Abraão Maia Ponciano</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>31987707291</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Abraham Nunes Santiago</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Abrahao Dias de Melo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1176217012</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Abrahão Romão da Silva</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>87988769998</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Abrahão Soares da Silva</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>35984246963</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Abraoo Raimundo Firmino de Lima</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>99991523978</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Acácio Gonçalves</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>24999443738</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Acácio Nascimento Junior</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>41992765311</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Acir Alves</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4291040962</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Adail Carvalho Sandoval</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>61984249737</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Adailton De Lima</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>31998436600</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Adailton Duarte Silva</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>64999348743</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Adailton Pereira dos Santos</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Adair Ordontis Dias</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>19983282161</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Adair Trindade dos Santos</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>31999312009</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Adalberon de Carvalho Garrett</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8186231412</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Adalberto Borges de Farias</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>64992292334</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Adalberto Do Amaral Ribeiro Taques</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>65981234961</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Adalberto Leandro Conceição</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>19982878523</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Adalberto Ribeiro</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Adalton Deboit Tomaz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>43999257623</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Adauto Cesar Da Silva</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>75988425464</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Adauto da Silva Gomes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>92984906006</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pastor</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Adauto Dantas do Amor Cardoso</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Não enviado</t>
         </is>
       </c>
     </row>
